--- a/data/dividends_info_20260512.xlsx
+++ b/data/dividends_info_20260512.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:K184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>49.60499954223633</v>
+        <v>47.67499923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1814333249280029</v>
+        <v>0.1887781886528857</v>
       </c>
       <c r="J2" t="n">
         <v>307</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.40000152587891</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.219512162703347</v>
+        <v>1.234567884622565</v>
       </c>
       <c r="J3" t="n">
         <v>286</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49.60499954223633</v>
+        <v>47.67499923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1814333249280029</v>
+        <v>0.1887781886528857</v>
       </c>
       <c r="J6" t="n">
         <v>216</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.065000057220459</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>3.728813455997861</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J7" t="n">
         <v>195</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.72999954223633</v>
+        <v>23.67000007629395</v>
       </c>
       <c r="I8" t="n">
-        <v>1.137800274793242</v>
+        <v>1.140684406969695</v>
       </c>
       <c r="J8" t="n">
         <v>195</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.809999942779541</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="I9" t="n">
-        <v>3.442340825640675</v>
+        <v>3.490401384542038</v>
       </c>
       <c r="J9" t="n">
         <v>188</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.449999809265137</v>
+        <v>6.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9302325856477186</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="J10" t="n">
         <v>160</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.9689922767163736</v>
       </c>
       <c r="J12" t="n">
         <v>146</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.96999979019165</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J13" t="n">
         <v>139</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.72500038146973</v>
+        <v>23.67000007629395</v>
       </c>
       <c r="I14" t="n">
-        <v>1.138040023851304</v>
+        <v>1.140684406969695</v>
       </c>
       <c r="J14" t="n">
         <v>132</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>49.60499954223633</v>
+        <v>47.67499923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1814333249280029</v>
+        <v>0.1887781886528857</v>
       </c>
       <c r="J15" t="n">
         <v>132</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4.96999979019165</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7615230810218038</v>
       </c>
       <c r="J17" t="n">
         <v>83</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.960000038146973</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="I18" t="n">
-        <v>4.194630845635492</v>
+        <v>4.18060199335474</v>
       </c>
       <c r="J18" t="n">
         <v>76</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.781999588012695</v>
+        <v>9.722000122070312</v>
       </c>
       <c r="I19" t="n">
-        <v>2.657943272852064</v>
+        <v>2.674346808634196</v>
       </c>
       <c r="J19" t="n">
         <v>69</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15.14000034332275</v>
+        <v>15.30000019073486</v>
       </c>
       <c r="I20" t="n">
-        <v>3.963011799168287</v>
+        <v>3.921568578563408</v>
       </c>
       <c r="J20" t="n">
         <v>69</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.742000102996826</v>
+        <v>3.618000030517578</v>
       </c>
       <c r="I21" t="n">
-        <v>5.879208817333017</v>
+        <v>6.080707521954542</v>
       </c>
       <c r="J21" t="n">
         <v>69</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.125</v>
+        <v>6.090000152587891</v>
       </c>
       <c r="I23" t="n">
-        <v>3.918367346938775</v>
+        <v>3.940886600766572</v>
       </c>
       <c r="J23" t="n">
         <v>69</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5.329999923706055</v>
+        <v>5.239999771118164</v>
       </c>
       <c r="I25" t="n">
-        <v>2.251407161682689</v>
+        <v>2.290076435907805</v>
       </c>
       <c r="J25" t="n">
         <v>62</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.309999942779541</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="I28" t="n">
-        <v>1.62412995195672</v>
+        <v>1.594533078107776</v>
       </c>
       <c r="J28" t="n">
         <v>55</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>35.70000076293945</v>
+        <v>35.29999923706055</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4201680582475409</v>
+        <v>0.4249291876542561</v>
       </c>
       <c r="J29" t="n">
         <v>55</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.800000190734863</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6896551497342619</v>
+        <v>0.7079645898200416</v>
       </c>
       <c r="J30" t="n">
         <v>48</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>23.52000045776367</v>
+        <v>23.42000007629395</v>
       </c>
       <c r="I31" t="n">
-        <v>4.039115567646243</v>
+        <v>4.056362070474984</v>
       </c>
       <c r="J31" t="n">
         <v>41</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>27.39999961853027</v>
+        <v>26.54999923706055</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7116788420249611</v>
+        <v>0.7344632979416583</v>
       </c>
       <c r="J32" t="n">
         <v>41</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.840000033378601</v>
+        <v>1.820000052452087</v>
       </c>
       <c r="I33" t="n">
-        <v>1.793478228334894</v>
+        <v>1.813186760931082</v>
       </c>
       <c r="J33" t="n">
         <v>41</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5.135000228881836</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>5.647516788195908</v>
+        <v>5.8</v>
       </c>
       <c r="J34" t="n">
         <v>41</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.871999979019165</v>
+        <v>3.845999956130981</v>
       </c>
       <c r="I35" t="n">
-        <v>4.132231427349604</v>
+        <v>4.160166454108793</v>
       </c>
       <c r="J35" t="n">
         <v>41</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.671999931335449</v>
+        <v>2.674000024795532</v>
       </c>
       <c r="I36" t="n">
-        <v>5.187125881800774</v>
+        <v>5.1832460252351</v>
       </c>
       <c r="J36" t="n">
         <v>41</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>50.59999847412109</v>
+        <v>49.99499893188477</v>
       </c>
       <c r="I37" t="n">
-        <v>1.245059326083197</v>
+        <v>1.260126039523149</v>
       </c>
       <c r="J37" t="n">
         <v>41</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>24.17000007629395</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="I40" t="n">
-        <v>3.516756298373719</v>
+        <v>3.525507998681073</v>
       </c>
       <c r="J40" t="n">
         <v>41</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>49.60499954223633</v>
+        <v>47.67499923706055</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1814333249280029</v>
+        <v>0.1887781886528857</v>
       </c>
       <c r="J41" t="n">
         <v>41</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.350000023841858</v>
+        <v>1.320000052452087</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7407407276587887</v>
+        <v>0.7575757274724028</v>
       </c>
       <c r="J42" t="n">
         <v>41</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.440000057220459</v>
+        <v>6.464000225067139</v>
       </c>
       <c r="I43" t="n">
-        <v>2.815217366290678</v>
+        <v>2.804764753827293</v>
       </c>
       <c r="J43" t="n">
         <v>41</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8.550000190734863</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="I44" t="n">
-        <v>3.040935604676908</v>
+        <v>3.044496500718773</v>
       </c>
       <c r="J44" t="n">
         <v>41</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>9.968000411987305</v>
+        <v>9.946000099182129</v>
       </c>
       <c r="I45" t="n">
-        <v>2.778892341004378</v>
+        <v>2.785039183970831</v>
       </c>
       <c r="J45" t="n">
         <v>41</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.696000099182129</v>
+        <v>3.730000019073486</v>
       </c>
       <c r="I47" t="n">
-        <v>2.976190396324432</v>
+        <v>2.949061647118261</v>
       </c>
       <c r="J47" t="n">
         <v>34</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.154999971389771</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="I49" t="n">
-        <v>5.071315418412519</v>
+        <v>5.128205316306579</v>
       </c>
       <c r="J49" t="n">
         <v>27</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.9049999713897705</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="I50" t="n">
-        <v>2.762431026556669</v>
+        <v>2.747252668077397</v>
       </c>
       <c r="J50" t="n">
         <v>27</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>27.45000076293945</v>
+        <v>27.5</v>
       </c>
       <c r="I51" t="n">
-        <v>4.043715734604362</v>
+        <v>4.036363636363636</v>
       </c>
       <c r="J51" t="n">
         <v>23</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9010000228881836</v>
+        <v>0.8980000019073486</v>
       </c>
       <c r="I52" t="n">
-        <v>3.329633655705586</v>
+        <v>3.340757231211593</v>
       </c>
       <c r="J52" t="n">
         <v>20</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.5109999775886536</v>
+        <v>0.5040000081062317</v>
       </c>
       <c r="I53" t="n">
-        <v>4.500978670984329</v>
+        <v>4.563491990093802</v>
       </c>
       <c r="J53" t="n">
         <v>20</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>19.79999923706055</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="I54" t="n">
-        <v>3.030303147067567</v>
+        <v>2.898550617805864</v>
       </c>
       <c r="J54" t="n">
         <v>20</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8.899999618530273</v>
+        <v>9</v>
       </c>
       <c r="I55" t="n">
-        <v>2.247191107554537</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="J55" t="n">
         <v>20</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.505000114440918</v>
+        <v>2.509999990463257</v>
       </c>
       <c r="I56" t="n">
-        <v>7.185628414239556</v>
+        <v>7.171314768283262</v>
       </c>
       <c r="J56" t="n">
         <v>13</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="I57" t="n">
-        <v>3.75</v>
+        <v>3.68098176738443</v>
       </c>
       <c r="J57" t="n">
         <v>13</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13.71000003814697</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="I58" t="n">
-        <v>1.823486501126149</v>
+        <v>1.816860434894887</v>
       </c>
       <c r="J58" t="n">
         <v>13</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.420000076293945</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8771929628875695</v>
+        <v>0.8595988515192625</v>
       </c>
       <c r="J59" t="n">
         <v>13</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.730000019073486</v>
+        <v>3.819999933242798</v>
       </c>
       <c r="I60" t="n">
-        <v>4.02144770061581</v>
+        <v>3.926701639302517</v>
       </c>
       <c r="J60" t="n">
         <v>13</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2.345999956130981</v>
+        <v>2.322999954223633</v>
       </c>
       <c r="I62" t="n">
-        <v>4.433077661753949</v>
+        <v>4.476969524295911</v>
       </c>
       <c r="J62" t="n">
         <v>6</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10.38000011444092</v>
+        <v>10.59500026702881</v>
       </c>
       <c r="I63" t="n">
-        <v>2.793834265922066</v>
+        <v>2.737140091468121</v>
       </c>
       <c r="J63" t="n">
         <v>6</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.065000057220459</v>
+        <v>2.045000076293945</v>
       </c>
       <c r="I64" t="n">
-        <v>3.728813455997861</v>
+        <v>3.765281033120711</v>
       </c>
       <c r="J64" t="n">
         <v>6</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>38.72000122070312</v>
+        <v>38.7599983215332</v>
       </c>
       <c r="I65" t="n">
-        <v>4.235537056551308</v>
+        <v>4.231166333897631</v>
       </c>
       <c r="J65" t="n">
         <v>6</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>36.09000015258789</v>
+        <v>35.61000061035156</v>
       </c>
       <c r="I66" t="n">
-        <v>5.541701278869589</v>
+        <v>5.616399791407515</v>
       </c>
       <c r="J66" t="n">
         <v>6</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3.752000093460083</v>
+        <v>3.757999897003174</v>
       </c>
       <c r="I67" t="n">
-        <v>2.665245136168968</v>
+        <v>2.660989961169111</v>
       </c>
       <c r="J67" t="n">
         <v>6</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>30.60000038146973</v>
+        <v>30.14999961853027</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4851633926446031</v>
+        <v>0.492404649679518</v>
       </c>
       <c r="J68" t="n">
         <v>6</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>20.63999938964844</v>
+        <v>20.65999984741211</v>
       </c>
       <c r="I69" t="n">
-        <v>4.457364472895319</v>
+        <v>4.453049403653505</v>
       </c>
       <c r="J69" t="n">
         <v>6</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>10.69999980926514</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I70" t="n">
-        <v>2.803738367735575</v>
+        <v>2.843601844324738</v>
       </c>
       <c r="J70" t="n">
         <v>6</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>81.87999725341797</v>
+        <v>82.05999755859375</v>
       </c>
       <c r="I71" t="n">
-        <v>1.270151483739317</v>
+        <v>1.267365380138359</v>
       </c>
       <c r="J71" t="n">
         <v>6</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>47</v>
+        <v>46.86000061035156</v>
       </c>
       <c r="I72" t="n">
-        <v>1.48936170212766</v>
+        <v>1.493811333509388</v>
       </c>
       <c r="J72" t="n">
         <v>6</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>57.40000152587891</v>
+        <v>56.70000076293945</v>
       </c>
       <c r="I73" t="n">
-        <v>3.832752511353377</v>
+        <v>3.880070494528063</v>
       </c>
       <c r="J73" t="n">
         <v>6</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>9.614999771118164</v>
+        <v>9.467000007629395</v>
       </c>
       <c r="I74" t="n">
-        <v>8.9443579872284</v>
+        <v>9.084187169186981</v>
       </c>
       <c r="J74" t="n">
         <v>6</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>12.39200019836426</v>
+        <v>12.24199962615967</v>
       </c>
       <c r="I75" t="n">
-        <v>4.519044472529302</v>
+        <v>4.574416084798337</v>
       </c>
       <c r="J75" t="n">
         <v>6</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2.180000066757202</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I76" t="n">
-        <v>1.834862329132901</v>
+        <v>1.843317907541938</v>
       </c>
       <c r="J76" t="n">
         <v>6</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.310000419616699</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="I77" t="n">
-        <v>3.222341422970111</v>
+        <v>3.205128322691611</v>
       </c>
       <c r="J77" t="n">
         <v>6</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.230000019073486</v>
+        <v>2.25</v>
       </c>
       <c r="I78" t="n">
-        <v>4.843049285931015</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>6</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>84.59999847412109</v>
+        <v>84.19999694824219</v>
       </c>
       <c r="I79" t="n">
-        <v>2.434988223587437</v>
+        <v>2.446555908150785</v>
       </c>
       <c r="J79" t="n">
         <v>6</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>15.73999977111816</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="I80" t="n">
-        <v>4.764930183647139</v>
+        <v>4.807692190128908</v>
       </c>
       <c r="J80" t="n">
         <v>6</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>14.64000034332275</v>
+        <v>14.84000015258789</v>
       </c>
       <c r="I81" t="n">
-        <v>2.049180279813509</v>
+        <v>2.021563321531935</v>
       </c>
       <c r="J81" t="n">
         <v>6</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>55</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I82" t="n">
-        <v>1.545454545454545</v>
+        <v>1.579925672962595</v>
       </c>
       <c r="J82" t="n">
         <v>6</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>33.88000106811523</v>
+        <v>36.38000106811523</v>
       </c>
       <c r="I83" t="n">
-        <v>2.508854702486838</v>
+        <v>2.336448529532813</v>
       </c>
       <c r="J83" t="n">
         <v>6</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>65.76000213623047</v>
+        <v>68.27999877929688</v>
       </c>
       <c r="I84" t="n">
-        <v>1.976885580549221</v>
+        <v>1.903925048683762</v>
       </c>
       <c r="J84" t="n">
         <v>6</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>7.940000057220459</v>
+        <v>8.020000457763672</v>
       </c>
       <c r="I85" t="n">
-        <v>7.556675008514306</v>
+        <v>7.481296331089067</v>
       </c>
       <c r="J85" t="n">
         <v>6</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>6.300000190734863</v>
+        <v>6.400000095367432</v>
       </c>
       <c r="I86" t="n">
-        <v>7.460317234453558</v>
+        <v>7.343749890569598</v>
       </c>
       <c r="J86" t="n">
         <v>6</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.809999942779541</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="I87" t="n">
-        <v>3.442340825640675</v>
+        <v>3.490401384542038</v>
       </c>
       <c r="J87" t="n">
         <v>6</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>23.39999961853027</v>
+        <v>22.92000007629395</v>
       </c>
       <c r="I88" t="n">
-        <v>4.273504343171475</v>
+        <v>4.363001730677547</v>
       </c>
       <c r="J88" t="n">
         <v>6</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.72500038146973</v>
+        <v>23.67000007629395</v>
       </c>
       <c r="I90" t="n">
-        <v>1.138040023851304</v>
+        <v>1.140684406969695</v>
       </c>
       <c r="J90" t="n">
         <v>6</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>8.260000228881836</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="I91" t="n">
-        <v>2.42130743895965</v>
+        <v>2.444987683844618</v>
       </c>
       <c r="J91" t="n">
         <v>6</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>21.69000053405762</v>
+        <v>21.46999931335449</v>
       </c>
       <c r="I93" t="n">
-        <v>3.642231353381217</v>
+        <v>3.679552982140128</v>
       </c>
       <c r="J93" t="n">
         <v>6</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5.260000228881836</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="I94" t="n">
-        <v>1.768060759567112</v>
+        <v>1.741572983943268</v>
       </c>
       <c r="J94" t="n">
         <v>6</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>6.449999809265137</v>
+        <v>6.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9302325856477186</v>
+        <v>0.923076923076923</v>
       </c>
       <c r="J95" t="n">
         <v>6</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>35.63999938964844</v>
+        <v>35.31999969482422</v>
       </c>
       <c r="I96" t="n">
-        <v>0.9820426655272524</v>
+        <v>0.990939985911973</v>
       </c>
       <c r="J96" t="n">
         <v>6</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.320000171661377</v>
+        <v>7.184999942779541</v>
       </c>
       <c r="I97" t="n">
-        <v>7.572404194004189</v>
+        <v>7.714683429566838</v>
       </c>
       <c r="J97" t="n">
         <v>6</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2.289999961853027</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I98" t="n">
-        <v>2.620087379890132</v>
+        <v>2.643171828376432</v>
       </c>
       <c r="J98" t="n">
         <v>6</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.954999923706055</v>
+        <v>6.885000228881836</v>
       </c>
       <c r="I100" t="n">
-        <v>1.48094897382997</v>
+        <v>1.496005759998759</v>
       </c>
       <c r="J100" t="n">
         <v>6</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5.769999980926514</v>
+        <v>5.776000022888184</v>
       </c>
       <c r="I101" t="n">
-        <v>3.292894291647656</v>
+        <v>3.289473671175541</v>
       </c>
       <c r="J101" t="n">
         <v>6</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>10.40999984741211</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I102" t="n">
-        <v>4.149855968608816</v>
+        <v>4.194174679614045</v>
       </c>
       <c r="J102" t="n">
         <v>6</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>26.20999908447266</v>
+        <v>26.57999992370605</v>
       </c>
       <c r="I103" t="n">
-        <v>1.678748627887839</v>
+        <v>1.655379989702614</v>
       </c>
       <c r="J103" t="n">
         <v>6</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1.019999980926514</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>2.941176525586755</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>6</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>8.300000190734863</v>
+        <v>8.260000228881836</v>
       </c>
       <c r="I105" t="n">
-        <v>5.662650472281341</v>
+        <v>5.690072481555177</v>
       </c>
       <c r="J105" t="n">
         <v>6</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>50.77999877929688</v>
+        <v>50.59999847412109</v>
       </c>
       <c r="I106" t="n">
-        <v>2.756991007590932</v>
+        <v>2.766798502407104</v>
       </c>
       <c r="J106" t="n">
         <v>6</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>3.967999935150146</v>
+        <v>3.910000085830688</v>
       </c>
       <c r="I107" t="n">
-        <v>7.560483994530312</v>
+        <v>7.672634102673282</v>
       </c>
       <c r="J107" t="n">
         <v>6</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>13.14999961853027</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9125475549892977</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J108" t="n">
         <v>6</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>21.45000076293945</v>
+        <v>21.75</v>
       </c>
       <c r="I110" t="n">
-        <v>3.263403147329649</v>
+        <v>3.218390804597701</v>
       </c>
       <c r="J110" t="n">
         <v>6</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2.359999895095825</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="I111" t="n">
-        <v>1.483050913380607</v>
+        <v>1.508620733065215</v>
       </c>
       <c r="J111" t="n">
         <v>6</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>5.809999942779541</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I112" t="n">
-        <v>5.679862362307114</v>
+        <v>5.769230980844901</v>
       </c>
       <c r="J112" t="n">
         <v>6</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.9769999980926514</v>
+        <v>0.9879999756813049</v>
       </c>
       <c r="I113" t="n">
-        <v>7.164790187989513</v>
+        <v>7.085020417306125</v>
       </c>
       <c r="J113" t="n">
         <v>6</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>49.52000045776367</v>
+        <v>49.81999969482422</v>
       </c>
       <c r="I114" t="n">
-        <v>1.433764122449008</v>
+        <v>1.42513047842062</v>
       </c>
       <c r="J114" t="n">
         <v>6</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>93.55000305175781</v>
+        <v>93.65000152587891</v>
       </c>
       <c r="I115" t="n">
-        <v>1.443078520535263</v>
+        <v>1.441537616661913</v>
       </c>
       <c r="J115" t="n">
         <v>6</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>7.099999904632568</v>
+        <v>7.019999980926514</v>
       </c>
       <c r="I116" t="n">
-        <v>1.126760578514967</v>
+        <v>1.13960114269746</v>
       </c>
       <c r="J116" t="n">
         <v>6</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="I117" t="n">
-        <v>1.239669421487603</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="J117" t="n">
         <v>6</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>4.452000141143799</v>
+        <v>4.461999893188477</v>
       </c>
       <c r="I118" t="n">
-        <v>3.818508414429743</v>
+        <v>3.80995078595846</v>
       </c>
       <c r="J118" t="n">
         <v>6</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>58.79999923706055</v>
+        <v>57.5</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7653061323789497</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="J120" t="n">
         <v>6</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5.239999771118164</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7633588119692684</v>
+        <v>0.7782101369459655</v>
       </c>
       <c r="J121" t="n">
         <v>6</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>37</v>
+        <v>37.36000061035156</v>
       </c>
       <c r="I122" t="n">
-        <v>2.837837837837838</v>
+        <v>2.81049245943821</v>
       </c>
       <c r="J122" t="n">
         <v>6</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>21.29999923706055</v>
+        <v>21.18000030517578</v>
       </c>
       <c r="I124" t="n">
-        <v>1.78403762258745</v>
+        <v>1.794145394356482</v>
       </c>
       <c r="J124" t="n">
         <v>6</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>26.77000045776367</v>
+        <v>26.45999908447266</v>
       </c>
       <c r="I125" t="n">
-        <v>2.241314866417911</v>
+        <v>2.267573774604149</v>
       </c>
       <c r="J125" t="n">
         <v>6</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>32.95000076293945</v>
+        <v>32.20000076293945</v>
       </c>
       <c r="I126" t="n">
-        <v>1.06221545340194</v>
+        <v>1.086956495985031</v>
       </c>
       <c r="J126" t="n">
         <v>6</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>3.660000085830688</v>
+        <v>3.700000047683716</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4644808634243957</v>
+        <v>0.45945945353818</v>
       </c>
       <c r="J127" t="n">
         <v>6</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.789999961853027</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3584229439687277</v>
+        <v>0.3484320696428174</v>
       </c>
       <c r="J128" t="n">
         <v>6</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>22.14999961853027</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="I129" t="n">
-        <v>5.05643349566033</v>
+        <v>5.063290947139111</v>
       </c>
       <c r="J129" t="n">
         <v>6</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1.590000033378601</v>
+        <v>1.580000042915344</v>
       </c>
       <c r="I130" t="n">
-        <v>6.289308044070249</v>
+        <v>6.329113752141711</v>
       </c>
       <c r="J130" t="n">
         <v>6</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>8.739999771118164</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I131" t="n">
-        <v>2.974828453190412</v>
+        <v>2.981651284840964</v>
       </c>
       <c r="J131" t="n">
         <v>6</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.124000072479248</v>
+        <v>2.104000091552734</v>
       </c>
       <c r="I132" t="n">
-        <v>4.345574239659156</v>
+        <v>4.38688193838829</v>
       </c>
       <c r="J132" t="n">
         <v>6</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>8.800000190734863</v>
+        <v>8.779999732971191</v>
       </c>
       <c r="I133" t="n">
-        <v>3.977272641067664</v>
+        <v>3.986332695269438</v>
       </c>
       <c r="J133" t="n">
         <v>-1</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>5.949999809265137</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I135" t="n">
-        <v>5.042016968350994</v>
+        <v>4.878048704844394</v>
       </c>
       <c r="J135" t="n">
         <v>-1</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>19.76000022888184</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="I138" t="n">
-        <v>2.5303643431602</v>
+        <v>2.551020358513417</v>
       </c>
       <c r="J138" t="n">
         <v>-1</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>2.200000047683716</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I139" t="n">
-        <v>2.727272668160684</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J139" t="n">
         <v>-1</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>15.5</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="I140" t="n">
-        <v>3.225806451612903</v>
+        <v>3.311258194493725</v>
       </c>
       <c r="J140" t="n">
         <v>-1</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>4.059999942779541</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="I141" t="n">
-        <v>2.463054221905688</v>
+        <v>2.427184533439133</v>
       </c>
       <c r="J141" t="n">
         <v>-1</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.579999923706055</v>
+        <v>3.529999971389771</v>
       </c>
       <c r="I142" t="n">
-        <v>3.072625763805235</v>
+        <v>3.116147334037873</v>
       </c>
       <c r="J142" t="n">
         <v>-1</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>7.059999942779541</v>
+        <v>6.989999771118164</v>
       </c>
       <c r="I148" t="n">
-        <v>3.116147334037873</v>
+        <v>3.147353465003153</v>
       </c>
       <c r="J148" t="n">
         <v>-1</v>
@@ -7400,11 +7400,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7428,14 +7428,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>3.019999980926514</v>
+        <v>27.14999961853027</v>
       </c>
       <c r="I149" t="n">
-        <v>4.966887448588033</v>
+        <v>2.246777195472467</v>
       </c>
       <c r="J149" t="n">
         <v>-8</v>
@@ -7447,11 +7447,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7475,14 +7475,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>11.10000038146973</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="I150" t="n">
-        <v>6.306306089579743</v>
+        <v>4.966887448588033</v>
       </c>
       <c r="J150" t="n">
         <v>-8</v>
@@ -7494,11 +7494,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5105</v>
+        <v>0.7</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7522,14 +7522,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>8.470000267028809</v>
+        <v>10.89999961853027</v>
       </c>
       <c r="I151" t="n">
-        <v>6.027154473503674</v>
+        <v>6.422018573376667</v>
       </c>
       <c r="J151" t="n">
         <v>-8</v>
@@ -7541,15 +7541,15 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.27</v>
+        <v>0.5105</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7569,14 +7569,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>8.329999923706055</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="I152" t="n">
-        <v>3.241296548294274</v>
+        <v>5.984759859097689</v>
       </c>
       <c r="J152" t="n">
         <v>-8</v>
@@ -7588,15 +7588,15 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7616,14 +7616,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>6.144999980926514</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="I153" t="n">
-        <v>5.695687568533217</v>
+        <v>3.300733373190234</v>
       </c>
       <c r="J153" t="n">
         <v>-8</v>
@@ -7635,11 +7635,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.1</v>
+        <v>0.35</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>40</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I154" t="n">
-        <v>2.75</v>
+        <v>5.737705007736096</v>
       </c>
       <c r="J154" t="n">
         <v>-8</v>
@@ -7682,11 +7682,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7705,19 +7705,19 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>17.79999923706055</v>
+        <v>40</v>
       </c>
       <c r="I155" t="n">
-        <v>4.213483326664756</v>
+        <v>2.75</v>
       </c>
       <c r="J155" t="n">
         <v>-8</v>
@@ -7729,11 +7729,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -7752,19 +7752,19 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>11.10000038146973</v>
+        <v>17.85000038146973</v>
       </c>
       <c r="I156" t="n">
-        <v>3.873873740741841</v>
+        <v>4.20168058247541</v>
       </c>
       <c r="J156" t="n">
         <v>-8</v>
@@ -7776,11 +7776,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7804,14 +7804,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>4.105000019073486</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="I157" t="n">
-        <v>3.654080372790243</v>
+        <v>3.873873740741841</v>
       </c>
       <c r="J157" t="n">
         <v>-8</v>
@@ -7823,11 +7823,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.197169</v>
+        <v>0.15</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>12.10000038146973</v>
+        <v>4.110000133514404</v>
       </c>
       <c r="I158" t="n">
-        <v>1.629495816396419</v>
+        <v>3.649634917937024</v>
       </c>
       <c r="J158" t="n">
         <v>-8</v>
@@ -7870,11 +7870,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1.1</v>
+        <v>0.197169</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7898,14 +7898,14 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>28.54999923706055</v>
+        <v>12.11999988555908</v>
       </c>
       <c r="I159" t="n">
-        <v>3.852889770210915</v>
+        <v>1.626806946053901</v>
       </c>
       <c r="J159" t="n">
         <v>-8</v>
@@ -7917,11 +7917,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.47</v>
+        <v>1.1</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7945,14 +7945,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>60.5</v>
+        <v>28.35000038146973</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7768595041322314</v>
+        <v>3.880070494528063</v>
       </c>
       <c r="J160" t="n">
         <v>-8</v>
@@ -7964,11 +7964,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.2</v>
+        <v>0.47</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7992,14 +7992,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>87.5</v>
+        <v>59.70000076293945</v>
       </c>
       <c r="I161" t="n">
-        <v>1.371428571428571</v>
+        <v>0.7872696716810871</v>
       </c>
       <c r="J161" t="n">
         <v>-8</v>
@@ -8011,11 +8011,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.27</v>
+        <v>1.2</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8039,14 +8039,14 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>25.14999961853027</v>
+        <v>88</v>
       </c>
       <c r="I162" t="n">
-        <v>1.073558664394836</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="J162" t="n">
         <v>-8</v>
@@ -8058,11 +8058,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8086,14 +8086,14 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>10.30000019073486</v>
+        <v>25.14999961853027</v>
       </c>
       <c r="I163" t="n">
-        <v>3.689320320030873</v>
+        <v>1.073558664394836</v>
       </c>
       <c r="J163" t="n">
         <v>-8</v>
@@ -8105,11 +8105,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8133,14 +8133,14 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>29.60000038146973</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I164" t="n">
-        <v>1.013513500451868</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J164" t="n">
         <v>-8</v>
@@ -8152,11 +8152,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8180,30 +8180,30 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>7.21999979019165</v>
+        <v>30</v>
       </c>
       <c r="I165" t="n">
-        <v>6.925207957474577</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
       <c r="K165" t="n">
-        <v>-20</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.65</v>
+        <v>0.007</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -8212,12 +8212,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8227,30 +8227,30 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>IT0004776628</t>
+          <t>IT0001073045</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>19.48500061035156</v>
+        <v>0.1695999950170517</v>
       </c>
       <c r="I166" t="n">
-        <v>3.335899305308116</v>
+        <v>4.127358611830275</v>
       </c>
       <c r="J166" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="K166" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -8259,12 +8259,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8274,30 +8274,30 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0001033700</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>12.95499992370605</v>
+        <v>6.940000057220459</v>
       </c>
       <c r="I167" t="n">
-        <v>4.168274821923129</v>
+        <v>2.305475485314068</v>
       </c>
       <c r="J167" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="K167" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.1</v>
+        <v>0.065</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -8306,12 +8306,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8321,30 +8321,30 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0003372205</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>5.434000015258789</v>
+        <v>2.115000009536743</v>
       </c>
       <c r="I168" t="n">
-        <v>1.840264992992231</v>
+        <v>3.073286038151707</v>
       </c>
       <c r="J168" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="K168" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8368,30 +8368,30 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0003365613</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>8.260000228881836</v>
+        <v>7.420000076293945</v>
       </c>
       <c r="I169" t="n">
-        <v>1.93704595116772</v>
+        <v>3.369272202553225</v>
       </c>
       <c r="J169" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="K169" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>3.615</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -8400,12 +8400,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8415,30 +8415,30 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>NL0011585146</t>
+          <t>IT0005549255</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>276.0499877929688</v>
+        <v>1.299999952316284</v>
       </c>
       <c r="I170" t="n">
-        <v>1.309545430123753</v>
+        <v>5.384615582121908</v>
       </c>
       <c r="J170" t="n">
-        <v>-22</v>
+        <v>-15</v>
       </c>
       <c r="K170" t="n">
-        <v>-7</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1.36</v>
+        <v>0.5</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -8462,14 +8462,14 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>IT0005144784</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H171" t="n">
-        <v>29</v>
+        <v>7.25</v>
       </c>
       <c r="I171" t="n">
-        <v>4.689655172413794</v>
+        <v>6.896551724137931</v>
       </c>
       <c r="J171" t="n">
         <v>-22</v>
@@ -8481,11 +8481,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>5.8216</v>
+        <v>0.65</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -8504,19 +8504,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>NL0015000LU4</t>
+          <t>IT0004776628</t>
         </is>
       </c>
       <c r="H172" t="n">
-        <v>13.91499996185303</v>
+        <v>19.36000061035156</v>
       </c>
       <c r="I172" t="n">
-        <v>41.8368668053144</v>
+        <v>3.357437910680916</v>
       </c>
       <c r="J172" t="n">
         <v>-22</v>
@@ -8528,11 +8528,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.14</v>
+        <v>0.54</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -8541,12 +8541,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8556,66 +8556,536 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>IT0001214433</t>
+          <t>IT0005218380</t>
         </is>
       </c>
       <c r="H173" t="n">
-        <v>26.5</v>
+        <v>13.13500022888184</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5283018867924528</v>
+        <v>4.111153335289812</v>
       </c>
       <c r="J173" t="n">
-        <v>-29</v>
+        <v>-22</v>
       </c>
       <c r="K173" t="n">
-        <v>-27</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>NL0015435975</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>5.372000217437744</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1.86150401996254</v>
+      </c>
+      <c r="J174" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K174" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>IT0005215329</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>8.220000267028809</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1.946471956233079</v>
+      </c>
+      <c r="J175" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K175" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>NL0011585146</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>280</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1.291071428571429</v>
+      </c>
+      <c r="J176" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K176" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>IT0005144784</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>29</v>
+      </c>
+      <c r="I177" t="n">
+        <v>4.689655172413794</v>
+      </c>
+      <c r="J177" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K177" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Iveco Group N.V.</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>5.8216</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Straordinario</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>NL0015000LU4</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>13.91499996185303</v>
+      </c>
+      <c r="I178" t="n">
+        <v>41.8368668053144</v>
+      </c>
+      <c r="J178" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K178" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>IT0004931058</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>14.8100004196167</v>
+      </c>
+      <c r="I179" t="n">
+        <v>3.950033649054687</v>
+      </c>
+      <c r="J179" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>IT0000062957</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>20.72999954223633</v>
+      </c>
+      <c r="I180" t="n">
+        <v>3.039073873187536</v>
+      </c>
+      <c r="J180" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>IT0004176001</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>148.8000030517578</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.6048386972727069</v>
+      </c>
+      <c r="J181" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K181" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Unicredit S.p.A.</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1.7208</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>IT0005239360</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>70.11000061035156</v>
+      </c>
+      <c r="I182" t="n">
+        <v>2.454428733446521</v>
+      </c>
+      <c r="J182" t="n">
+        <v>-22</v>
+      </c>
+      <c r="K182" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>IT0001214433</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="J183" t="n">
+        <v>-29</v>
+      </c>
+      <c r="K183" t="n">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
           <t>Reti S.p.A.</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B184" t="n">
         <v>0.06</v>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
         <is>
           <t>IT0005418204</t>
         </is>
       </c>
-      <c r="H174" t="n">
-        <v>1.490000009536743</v>
-      </c>
-      <c r="I174" t="n">
-        <v>4.026845611810072</v>
-      </c>
-      <c r="J174" t="n">
+      <c r="H184" t="n">
+        <v>1.470000028610229</v>
+      </c>
+      <c r="I184" t="n">
+        <v>4.081632573621466</v>
+      </c>
+      <c r="J184" t="n">
         <v>-29</v>
       </c>
-      <c r="K174" t="n">
+      <c r="K184" t="n">
         <v>-27</v>
       </c>
     </row>
@@ -9921,14 +10391,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9945,7 +10415,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -9955,14 +10425,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9972,14 +10442,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9989,14 +10459,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10006,14 +10476,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10030,7 +10500,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10047,7 +10517,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10057,7 +10527,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10568,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10115,7 +10585,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10125,14 +10595,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10142,7 +10612,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10636,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10200,7 +10670,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10217,7 +10687,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10234,7 +10704,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10251,7 +10721,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10268,7 +10738,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10278,14 +10748,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10295,14 +10765,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10319,7 +10789,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10336,7 +10806,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10404,7 +10874,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10421,7 +10891,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10438,7 +10908,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10455,7 +10925,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10472,7 +10942,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10489,7 +10959,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10506,7 +10976,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10540,7 +11010,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10557,7 +11027,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10567,14 +11037,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10584,14 +11054,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10608,7 +11078,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10625,7 +11095,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10635,7 +11105,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10652,14 +11122,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10676,7 +11146,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10686,14 +11156,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10703,14 +11173,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10720,14 +11190,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10737,14 +11207,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10754,14 +11224,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10778,7 +11248,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10788,14 +11258,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10805,14 +11275,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10822,14 +11292,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10839,14 +11309,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10863,7 +11333,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10873,14 +11343,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10897,7 +11367,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10914,7 +11384,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10931,7 +11401,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10965,7 +11435,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10975,14 +11445,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10992,7 +11462,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11486,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11026,14 +11496,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11067,7 +11537,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11077,14 +11547,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11101,7 +11571,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11118,7 +11588,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11128,14 +11598,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11169,7 +11639,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11179,14 +11649,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11196,14 +11666,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11213,14 +11683,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11230,14 +11700,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11247,14 +11717,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11271,7 +11741,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11288,7 +11758,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11298,14 +11768,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11315,14 +11785,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11332,14 +11802,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11349,14 +11819,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11366,14 +11836,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11390,7 +11860,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11400,14 +11870,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11417,14 +11887,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11441,7 +11911,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11451,14 +11921,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11468,14 +11938,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11485,7 +11955,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11979,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11519,14 +11989,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11536,14 +12006,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11553,14 +12023,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11570,14 +12040,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11587,14 +12057,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11604,14 +12074,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11621,14 +12091,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11645,7 +12115,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11655,14 +12125,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11672,7 +12142,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11713,7 +12183,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11730,7 +12200,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11740,14 +12210,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11764,7 +12234,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11774,7 +12244,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11798,7 +12268,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11815,7 +12285,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11849,7 +12319,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11866,7 +12336,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11883,7 +12353,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11900,7 +12370,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11917,7 +12387,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11927,14 +12397,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11944,7 +12414,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11968,7 +12438,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11978,14 +12448,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11995,7 +12465,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12489,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12029,14 +12499,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12053,7 +12523,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12070,7 +12540,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12087,7 +12557,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12097,14 +12567,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12114,14 +12584,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12138,7 +12608,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12155,7 +12625,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12172,7 +12642,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12189,7 +12659,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12223,7 +12693,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12233,14 +12703,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12250,14 +12720,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12267,14 +12737,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12291,7 +12761,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12308,7 +12778,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12325,7 +12795,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12335,14 +12805,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12352,14 +12822,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12369,7 +12839,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12863,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12403,14 +12873,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12420,14 +12890,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12437,14 +12907,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12461,7 +12931,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12471,14 +12941,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12597,7 +13067,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12631,7 +13101,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12716,7 +13186,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12750,7 +13220,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12767,7 +13237,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12777,14 +13247,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12794,14 +13264,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12818,7 +13288,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12852,7 +13322,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12862,14 +13332,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12879,7 +13349,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -12907,146 +13377,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Abitare In S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>IDNTT S.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IDNTT S.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>